--- a/tests/fixtures/11_loan_schedule/11_loan_schedule_pattern-from-claude.xlsx
+++ b/tests/fixtures/11_loan_schedule/11_loan_schedule_pattern-from-claude.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
@@ -991,36 +991,40 @@
       <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>col_totals</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>loan_amount_label</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1030,7 +1034,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>loan.amount</t>
+          <t>loan_amount_label</t>
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>monthly_rate_label</t>
+          <t>loan.amount</t>
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
@@ -1066,7 +1070,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>loan.monthly_rate</t>
+          <t>monthly_rate_label</t>
         </is>
       </c>
       <c r="C27" s="5" t="n"/>
@@ -1084,7 +1088,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>term_label</t>
+          <t>loan.monthly_rate</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -1102,7 +1106,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>loan.term_months</t>
+          <t>term_label</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
@@ -1120,7 +1124,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>start_date_label</t>
+          <t>loan.term_months</t>
         </is>
       </c>
       <c r="C30" s="5" t="n"/>
@@ -1138,7 +1142,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>loan.start_date</t>
+          <t>start_date_label</t>
         </is>
       </c>
       <c r="C31" s="5" t="n"/>
@@ -1149,108 +1153,164 @@
       <c r="H31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>loan.start_date</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>payment_num_header</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>date_header</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>payment_header</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>principal_header</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>interest_header</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>balance_header</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="n"/>
-      <c r="B34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>payment.number</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>payment.date</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>payment.amount</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>payment.principal</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>payment.interest</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>payment.balance</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FOOTER:1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>col_totals</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
